--- a/01-进度计划/月度计划表/2026.09/电站9月度工作计划表_王景处.xlsx
+++ b/01-进度计划/月度计划表/2026.09/电站9月度工作计划表_王景处.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="27950" windowHeight="14080"/>
+    <workbookView windowWidth="23150" windowHeight="14080"/>
   </bookViews>
   <sheets>
     <sheet name="9月度计划明细表（总）" sheetId="1" r:id="rId1"/>
@@ -2194,9 +2194,9 @@
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="10.9090909090909" style="38" customWidth="1"/>
-    <col min="2" max="2" width="19.6272727272727" style="38" customWidth="1"/>
-    <col min="3" max="3" width="21.6272727272727" style="38" customWidth="1"/>
-    <col min="4" max="4" width="31.7090909090909" style="38" customWidth="1"/>
+    <col min="2" max="2" width="12.0909090909091" style="38" customWidth="1"/>
+    <col min="3" max="3" width="9.54545454545454" style="38" customWidth="1"/>
+    <col min="4" max="4" width="17.3636363636364" style="38" customWidth="1"/>
     <col min="5" max="5" width="16.5363636363636" style="38" customWidth="1"/>
     <col min="6" max="6" width="14.3727272727273" style="38" customWidth="1"/>
     <col min="7" max="7" width="16.4636363636364" style="38" customWidth="1"/>
@@ -2313,7 +2313,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="4" ht="31" customHeight="1" spans="1:16">
+    <row r="4" ht="28" customHeight="1" spans="1:16">
       <c r="A4" s="56">
         <v>1</v>
       </c>
@@ -2345,7 +2345,7 @@
       <c r="O4" s="59"/>
       <c r="P4" s="60"/>
     </row>
-    <row r="5" ht="31" customHeight="1" spans="1:16">
+    <row r="5" ht="28" customHeight="1" spans="1:16">
       <c r="A5" s="56">
         <v>2</v>
       </c>
@@ -2377,7 +2377,7 @@
       <c r="O5" s="59"/>
       <c r="P5" s="60"/>
     </row>
-    <row r="6" ht="31" customHeight="1" spans="1:16">
+    <row r="6" ht="28" customHeight="1" spans="1:16">
       <c r="A6" s="56">
         <v>3</v>
       </c>
@@ -2413,7 +2413,7 @@
       <c r="O6" s="59"/>
       <c r="P6" s="60"/>
     </row>
-    <row r="7" ht="31" customHeight="1" spans="1:16">
+    <row r="7" ht="28" customHeight="1" spans="1:16">
       <c r="A7" s="56">
         <v>4</v>
       </c>
@@ -2445,7 +2445,7 @@
       <c r="O7" s="59"/>
       <c r="P7" s="60"/>
     </row>
-    <row r="8" ht="31" customHeight="1" spans="1:16">
+    <row r="8" ht="28" customHeight="1" spans="1:16">
       <c r="A8" s="56">
         <v>5</v>
       </c>
@@ -2481,7 +2481,7 @@
       <c r="O8" s="59"/>
       <c r="P8" s="60"/>
     </row>
-    <row r="9" ht="31" customHeight="1" spans="1:16">
+    <row r="9" ht="28" customHeight="1" spans="1:16">
       <c r="A9" s="56">
         <v>6</v>
       </c>
@@ -2517,7 +2517,7 @@
       <c r="O9" s="59"/>
       <c r="P9" s="60"/>
     </row>
-    <row r="10" ht="31" customHeight="1" spans="1:16">
+    <row r="10" ht="28" customHeight="1" spans="1:16">
       <c r="A10" s="56">
         <v>7</v>
       </c>
@@ -2561,7 +2561,7 @@
       <c r="O10" s="59"/>
       <c r="P10" s="60"/>
     </row>
-    <row r="11" ht="31" customHeight="1" spans="1:16">
+    <row r="11" ht="28" customHeight="1" spans="1:16">
       <c r="A11" s="56">
         <v>8</v>
       </c>
@@ -2605,7 +2605,7 @@
       <c r="O11" s="59"/>
       <c r="P11" s="60"/>
     </row>
-    <row r="12" ht="31" customHeight="1" spans="1:16">
+    <row r="12" ht="28" customHeight="1" spans="1:16">
       <c r="A12" s="56">
         <v>9</v>
       </c>
@@ -2649,7 +2649,7 @@
       <c r="O12" s="59"/>
       <c r="P12" s="60"/>
     </row>
-    <row r="13" ht="31" customHeight="1" spans="1:16">
+    <row r="13" ht="28" customHeight="1" spans="1:16">
       <c r="A13" s="56">
         <v>10</v>
       </c>
@@ -2693,7 +2693,7 @@
       <c r="O13" s="59"/>
       <c r="P13" s="60"/>
     </row>
-    <row r="14" s="38" customFormat="1" ht="20" customHeight="1" spans="1:16">
+    <row r="14" s="38" customFormat="1" ht="28" customHeight="1" spans="1:16">
       <c r="A14" s="56">
         <v>11</v>
       </c>
@@ -2719,7 +2719,7 @@
       <c r="O14" s="59"/>
       <c r="P14" s="60"/>
     </row>
-    <row r="15" s="38" customFormat="1" ht="20" customHeight="1" spans="1:16">
+    <row r="15" s="38" customFormat="1" ht="28" customHeight="1" spans="1:16">
       <c r="A15" s="56">
         <v>12</v>
       </c>
@@ -2741,7 +2741,7 @@
       <c r="O15" s="59"/>
       <c r="P15" s="60"/>
     </row>
-    <row r="16" s="38" customFormat="1" ht="20" customHeight="1" spans="1:16">
+    <row r="16" s="38" customFormat="1" ht="28" customHeight="1" spans="1:16">
       <c r="A16" s="56">
         <v>13</v>
       </c>
@@ -2787,7 +2787,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="17" s="38" customFormat="1" ht="20" customHeight="1" spans="1:16">
+    <row r="17" s="38" customFormat="1" ht="28" customHeight="1" spans="1:16">
       <c r="A17" s="56">
         <v>14</v>
       </c>
@@ -2813,7 +2813,7 @@
       <c r="O17" s="59"/>
       <c r="P17" s="60"/>
     </row>
-    <row r="18" s="38" customFormat="1" ht="20" customHeight="1" spans="1:16">
+    <row r="18" s="38" customFormat="1" ht="28" customHeight="1" spans="1:16">
       <c r="A18" s="56">
         <v>15</v>
       </c>
@@ -2835,7 +2835,7 @@
       <c r="O18" s="59"/>
       <c r="P18" s="60"/>
     </row>
-    <row r="19" s="38" customFormat="1" ht="20" customHeight="1" spans="1:16">
+    <row r="19" s="38" customFormat="1" ht="28" customHeight="1" spans="1:16">
       <c r="A19" s="56">
         <v>16</v>
       </c>
@@ -2871,7 +2871,7 @@
       <c r="O19" s="59"/>
       <c r="P19" s="60"/>
     </row>
-    <row r="20" s="38" customFormat="1" ht="20" customHeight="1" spans="1:16">
+    <row r="20" s="38" customFormat="1" ht="28" customHeight="1" spans="1:16">
       <c r="A20" s="56">
         <v>17</v>
       </c>
@@ -2901,7 +2901,7 @@
       <c r="O20" s="59"/>
       <c r="P20" s="60"/>
     </row>
-    <row r="21" s="38" customFormat="1" ht="20" customHeight="1" spans="1:16">
+    <row r="21" s="38" customFormat="1" ht="28" customHeight="1" spans="1:16">
       <c r="A21" s="56">
         <v>18</v>
       </c>
@@ -2927,7 +2927,7 @@
       <c r="O21" s="59"/>
       <c r="P21" s="60"/>
     </row>
-    <row r="22" s="38" customFormat="1" ht="20" customHeight="1" spans="1:16">
+    <row r="22" s="38" customFormat="1" ht="28" customHeight="1" spans="1:16">
       <c r="A22" s="56">
         <v>19</v>
       </c>
@@ -2957,7 +2957,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="23" s="38" customFormat="1" ht="20" customHeight="1" spans="1:16">
+    <row r="23" s="38" customFormat="1" ht="28" customHeight="1" spans="1:16">
       <c r="A23" s="56">
         <v>20</v>
       </c>
@@ -2995,7 +2995,7 @@
       <c r="O23" s="59"/>
       <c r="P23" s="60"/>
     </row>
-    <row r="24" s="38" customFormat="1" ht="20" customHeight="1" spans="1:16">
+    <row r="24" s="38" customFormat="1" ht="28" customHeight="1" spans="1:16">
       <c r="A24" s="56">
         <v>21</v>
       </c>
@@ -3021,7 +3021,7 @@
       <c r="O24" s="59"/>
       <c r="P24" s="60"/>
     </row>
-    <row r="25" s="38" customFormat="1" ht="20" customHeight="1" spans="1:16">
+    <row r="25" s="38" customFormat="1" ht="28" customHeight="1" spans="1:16">
       <c r="A25" s="56">
         <v>22</v>
       </c>
@@ -3051,7 +3051,7 @@
       </c>
       <c r="P25" s="66"/>
     </row>
-    <row r="26" s="38" customFormat="1" ht="20" customHeight="1" spans="1:16">
+    <row r="26" s="38" customFormat="1" ht="28" customHeight="1" spans="1:16">
       <c r="A26" s="56">
         <v>23</v>
       </c>
@@ -3087,7 +3087,7 @@
       <c r="O26" s="65"/>
       <c r="P26" s="66"/>
     </row>
-    <row r="27" s="38" customFormat="1" ht="20" customHeight="1" spans="1:16">
+    <row r="27" s="38" customFormat="1" ht="28" customHeight="1" spans="1:16">
       <c r="A27" s="56">
         <v>24</v>
       </c>
@@ -3115,7 +3115,7 @@
       <c r="O27" s="59"/>
       <c r="P27" s="60"/>
     </row>
-    <row r="28" s="39" customFormat="1" ht="19" customHeight="1" spans="1:16">
+    <row r="28" s="39" customFormat="1" ht="28" customHeight="1" spans="1:16">
       <c r="A28" s="56">
         <v>25</v>
       </c>
@@ -3139,7 +3139,7 @@
       <c r="O28" s="67"/>
       <c r="P28" s="68"/>
     </row>
-    <row r="29" s="39" customFormat="1" ht="19" customHeight="1" spans="1:16">
+    <row r="29" s="39" customFormat="1" ht="28" customHeight="1" spans="1:16">
       <c r="A29" s="56">
         <v>26</v>
       </c>
@@ -3177,7 +3177,7 @@
       <c r="O29" s="67"/>
       <c r="P29" s="68"/>
     </row>
-    <row r="30" s="39" customFormat="1" ht="19" customHeight="1" spans="1:16">
+    <row r="30" s="39" customFormat="1" ht="28" customHeight="1" spans="1:16">
       <c r="A30" s="56">
         <v>27</v>
       </c>
@@ -3207,7 +3207,7 @@
       </c>
       <c r="P30" s="71"/>
     </row>
-    <row r="31" s="39" customFormat="1" ht="19" customHeight="1" spans="1:16">
+    <row r="31" s="39" customFormat="1" ht="28" customHeight="1" spans="1:16">
       <c r="A31" s="56">
         <v>28</v>
       </c>
@@ -3237,7 +3237,7 @@
       <c r="O31" s="70"/>
       <c r="P31" s="71"/>
     </row>
-    <row r="32" s="39" customFormat="1" ht="19" customHeight="1" spans="1:16">
+    <row r="32" s="39" customFormat="1" ht="28" customHeight="1" spans="1:16">
       <c r="A32" s="56">
         <v>29</v>
       </c>
@@ -3261,7 +3261,7 @@
       <c r="O32" s="70"/>
       <c r="P32" s="71"/>
     </row>
-    <row r="33" s="39" customFormat="1" ht="19" customHeight="1" spans="1:16">
+    <row r="33" s="39" customFormat="1" ht="28" customHeight="1" spans="1:16">
       <c r="A33" s="56">
         <v>30</v>
       </c>
@@ -3295,7 +3295,7 @@
       <c r="O33" s="70"/>
       <c r="P33" s="71"/>
     </row>
-    <row r="34" s="39" customFormat="1" ht="19" customHeight="1" spans="1:16">
+    <row r="34" s="39" customFormat="1" ht="28" customHeight="1" spans="1:16">
       <c r="A34" s="56">
         <v>31</v>
       </c>
@@ -3325,7 +3325,7 @@
       <c r="O34" s="70"/>
       <c r="P34" s="71"/>
     </row>
-    <row r="35" s="39" customFormat="1" ht="19" customHeight="1" spans="1:16">
+    <row r="35" s="39" customFormat="1" ht="28" customHeight="1" spans="1:16">
       <c r="A35" s="56">
         <v>32</v>
       </c>
@@ -3349,7 +3349,7 @@
       <c r="O35" s="70"/>
       <c r="P35" s="71"/>
     </row>
-    <row r="36" s="39" customFormat="1" ht="19" customHeight="1" spans="1:16">
+    <row r="36" s="39" customFormat="1" ht="28" customHeight="1" spans="1:16">
       <c r="A36" s="56">
         <v>33</v>
       </c>
@@ -3383,7 +3383,7 @@
       <c r="O36" s="70"/>
       <c r="P36" s="71"/>
     </row>
-    <row r="37" s="39" customFormat="1" ht="19" customHeight="1" spans="1:16">
+    <row r="37" s="39" customFormat="1" ht="28" customHeight="1" spans="1:16">
       <c r="A37" s="56">
         <v>34</v>
       </c>
@@ -3413,7 +3413,7 @@
       <c r="O37" s="70"/>
       <c r="P37" s="71"/>
     </row>
-    <row r="38" s="39" customFormat="1" ht="19" customHeight="1" spans="1:16">
+    <row r="38" s="39" customFormat="1" ht="28" customHeight="1" spans="1:16">
       <c r="A38" s="56">
         <v>35</v>
       </c>
@@ -3437,7 +3437,7 @@
       <c r="O38" s="70"/>
       <c r="P38" s="71"/>
     </row>
-    <row r="39" s="39" customFormat="1" ht="19" customHeight="1" spans="1:16">
+    <row r="39" s="39" customFormat="1" ht="28" customHeight="1" spans="1:16">
       <c r="A39" s="56">
         <v>36</v>
       </c>
@@ -3471,7 +3471,7 @@
       <c r="O39" s="70"/>
       <c r="P39" s="71"/>
     </row>
-    <row r="40" s="40" customFormat="1" ht="19" customHeight="1" spans="1:16">
+    <row r="40" s="40" customFormat="1" ht="28" customHeight="1" spans="1:16">
       <c r="A40" s="56">
         <v>37</v>
       </c>

--- a/01-进度计划/月度计划表/2026.09/电站9月度工作计划表_王景处.xlsx
+++ b/01-进度计划/月度计划表/2026.09/电站9月度工作计划表_王景处.xlsx
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="403" uniqueCount="158">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="389" uniqueCount="158">
   <si>
     <r>
       <rPr>
@@ -165,25 +165,25 @@
     <t>脱硫塔安装</t>
   </si>
   <si>
+    <t>除尘器安装</t>
+  </si>
+  <si>
+    <t>电气仪表</t>
+  </si>
+  <si>
+    <t>设备采购</t>
+  </si>
+  <si>
+    <t>低压开关柜采购前期技术交流</t>
+  </si>
+  <si>
+    <t>低压开关柜采商务洽谈及订货</t>
+  </si>
+  <si>
+    <t>低压开关柜生产</t>
+  </si>
+  <si>
     <t>持续</t>
-  </si>
-  <si>
-    <t>除尘器安装</t>
-  </si>
-  <si>
-    <t>电气仪表</t>
-  </si>
-  <si>
-    <t>设备采购</t>
-  </si>
-  <si>
-    <t>低压开关柜采购前期技术交流</t>
-  </si>
-  <si>
-    <t>低压开关柜采商务洽谈及订货</t>
-  </si>
-  <si>
-    <t>低压开关柜生产</t>
   </si>
   <si>
     <t>采购</t>
@@ -550,7 +550,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="32">
+  <fonts count="33">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -599,6 +599,12 @@
     </font>
     <font>
       <sz val="10"/>
+      <name val="微软雅黑"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FFFF0000"/>
       <name val="微软雅黑"/>
       <charset val="134"/>
     </font>
@@ -1384,137 +1390,137 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="21" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="22" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="22" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="23" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="22" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="23" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="8" borderId="24" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="9" borderId="25" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="8" borderId="24" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="9" borderId="24" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="9" borderId="25" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="10" borderId="26" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="9" borderId="24" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="27" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="10" borderId="26" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="28" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="27" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="28" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="28" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="29" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="30" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="31" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="31" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="30" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="30" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="31" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="31" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="30" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="30" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="31" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="31" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="30" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="30" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="31" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="31" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="30" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="30" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="31" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="31" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="30" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="30" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="31" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="31" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="30" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="95">
+  <cellXfs count="97">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -1688,12 +1694,18 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="58" fontId="7" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1718,40 +1730,40 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2197,15 +2209,11 @@
     <col min="2" max="2" width="12.0909090909091" style="38" customWidth="1"/>
     <col min="3" max="3" width="9.54545454545454" style="38" customWidth="1"/>
     <col min="4" max="4" width="17.3636363636364" style="38" customWidth="1"/>
-    <col min="5" max="5" width="16.5363636363636" style="38" customWidth="1"/>
-    <col min="6" max="6" width="14.3727272727273" style="38" customWidth="1"/>
-    <col min="7" max="7" width="16.4636363636364" style="38" customWidth="1"/>
-    <col min="8" max="11" width="14.6272727272727" style="38" customWidth="1"/>
-    <col min="12" max="12" width="16.5363636363636" style="38" customWidth="1"/>
-    <col min="13" max="13" width="12.5454545454545" style="38" customWidth="1"/>
-    <col min="14" max="14" width="12" style="38" customWidth="1"/>
-    <col min="15" max="15" width="30" style="38" customWidth="1"/>
-    <col min="16" max="16" width="60.0909090909091" style="38" customWidth="1"/>
+    <col min="5" max="12" width="9.32727272727273" style="38" customWidth="1"/>
+    <col min="13" max="13" width="7.34545454545455" style="38" customWidth="1"/>
+    <col min="14" max="14" width="8.85454545454546" style="38" customWidth="1"/>
+    <col min="15" max="15" width="8.84545454545455" style="38" customWidth="1"/>
+    <col min="16" max="16" width="24.1909090909091" style="38" customWidth="1"/>
     <col min="17" max="16384" width="9" style="38" customWidth="1"/>
   </cols>
   <sheetData>
@@ -2263,7 +2271,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="3" ht="22" customHeight="1" spans="1:16">
+    <row r="3" ht="50" customHeight="1" spans="1:16">
       <c r="A3" s="53" t="s">
         <v>9</v>
       </c>
@@ -2338,12 +2346,14 @@
       <c r="J4" s="57"/>
       <c r="K4" s="57"/>
       <c r="L4" s="57"/>
-      <c r="M4" s="57"/>
+      <c r="M4" s="59">
+        <v>100</v>
+      </c>
       <c r="N4" s="57" t="s">
         <v>22</v>
       </c>
-      <c r="O4" s="59"/>
-      <c r="P4" s="60"/>
+      <c r="O4" s="60"/>
+      <c r="P4" s="61"/>
     </row>
     <row r="5" ht="28" customHeight="1" spans="1:16">
       <c r="A5" s="56">
@@ -2370,12 +2380,14 @@
       <c r="J5" s="57"/>
       <c r="K5" s="57"/>
       <c r="L5" s="57"/>
-      <c r="M5" s="57"/>
+      <c r="M5" s="59">
+        <v>100</v>
+      </c>
       <c r="N5" s="57" t="s">
         <v>22</v>
       </c>
-      <c r="O5" s="59"/>
-      <c r="P5" s="60"/>
+      <c r="O5" s="60"/>
+      <c r="P5" s="61"/>
     </row>
     <row r="6" ht="28" customHeight="1" spans="1:16">
       <c r="A6" s="56">
@@ -2393,12 +2405,8 @@
       <c r="E6" s="57">
         <v>9.1</v>
       </c>
-      <c r="F6" s="57">
-        <v>9.5</v>
-      </c>
-      <c r="G6" s="57">
-        <v>9.6</v>
-      </c>
+      <c r="F6" s="57"/>
+      <c r="G6" s="57"/>
       <c r="H6" s="57">
         <v>9.11</v>
       </c>
@@ -2406,12 +2414,14 @@
       <c r="J6" s="57"/>
       <c r="K6" s="57"/>
       <c r="L6" s="57"/>
-      <c r="M6" s="57"/>
+      <c r="M6" s="59">
+        <v>100</v>
+      </c>
       <c r="N6" s="57" t="s">
         <v>22</v>
       </c>
-      <c r="O6" s="59"/>
-      <c r="P6" s="60"/>
+      <c r="O6" s="60"/>
+      <c r="P6" s="61"/>
     </row>
     <row r="7" ht="28" customHeight="1" spans="1:16">
       <c r="A7" s="56">
@@ -2438,12 +2448,14 @@
       <c r="J7" s="57"/>
       <c r="K7" s="57"/>
       <c r="L7" s="57"/>
-      <c r="M7" s="57"/>
+      <c r="M7" s="59">
+        <v>100</v>
+      </c>
       <c r="N7" s="57" t="s">
         <v>22</v>
       </c>
-      <c r="O7" s="59"/>
-      <c r="P7" s="60"/>
+      <c r="O7" s="60"/>
+      <c r="P7" s="61"/>
     </row>
     <row r="8" ht="28" customHeight="1" spans="1:16">
       <c r="A8" s="56">
@@ -2461,12 +2473,8 @@
       <c r="E8" s="57">
         <v>9.1</v>
       </c>
-      <c r="F8" s="57">
-        <v>9.5</v>
-      </c>
-      <c r="G8" s="57">
-        <v>9.6</v>
-      </c>
+      <c r="F8" s="57"/>
+      <c r="G8" s="57"/>
       <c r="H8" s="57">
         <v>9.11</v>
       </c>
@@ -2474,12 +2482,14 @@
       <c r="J8" s="57"/>
       <c r="K8" s="57"/>
       <c r="L8" s="57"/>
-      <c r="M8" s="57"/>
+      <c r="M8" s="59">
+        <v>100</v>
+      </c>
       <c r="N8" s="57" t="s">
         <v>22</v>
       </c>
-      <c r="O8" s="59"/>
-      <c r="P8" s="60"/>
+      <c r="O8" s="60"/>
+      <c r="P8" s="61"/>
     </row>
     <row r="9" ht="28" customHeight="1" spans="1:16">
       <c r="A9" s="56">
@@ -2497,12 +2507,8 @@
       <c r="E9" s="57">
         <v>9.1</v>
       </c>
-      <c r="F9" s="57">
-        <v>9.5</v>
-      </c>
-      <c r="G9" s="57">
-        <v>9.6</v>
-      </c>
+      <c r="F9" s="57"/>
+      <c r="G9" s="57"/>
       <c r="H9" s="57">
         <v>9.11</v>
       </c>
@@ -2510,12 +2516,14 @@
       <c r="J9" s="57"/>
       <c r="K9" s="57"/>
       <c r="L9" s="57"/>
-      <c r="M9" s="57"/>
+      <c r="M9" s="59">
+        <v>100</v>
+      </c>
       <c r="N9" s="57" t="s">
         <v>29</v>
       </c>
-      <c r="O9" s="59"/>
-      <c r="P9" s="60"/>
+      <c r="O9" s="60"/>
+      <c r="P9" s="61"/>
     </row>
     <row r="10" ht="28" customHeight="1" spans="1:16">
       <c r="A10" s="56">
@@ -2533,33 +2541,23 @@
       <c r="E10" s="57">
         <v>9.1</v>
       </c>
-      <c r="F10" s="57">
-        <v>9.5</v>
-      </c>
-      <c r="G10" s="57">
-        <v>9.6</v>
-      </c>
-      <c r="H10" s="57">
-        <v>9.11</v>
-      </c>
-      <c r="I10" s="57">
-        <v>9.12</v>
-      </c>
-      <c r="J10" s="57">
-        <v>9.18</v>
-      </c>
-      <c r="K10" s="57">
-        <v>9.19</v>
-      </c>
-      <c r="L10" s="57">
-        <v>9.25</v>
-      </c>
-      <c r="M10" s="57"/>
+      <c r="F10" s="57"/>
+      <c r="G10" s="57"/>
+      <c r="H10" s="57"/>
+      <c r="I10" s="57"/>
+      <c r="J10" s="57"/>
+      <c r="K10" s="57"/>
+      <c r="L10" s="62">
+        <v>46295</v>
+      </c>
+      <c r="M10" s="59">
+        <v>80</v>
+      </c>
       <c r="N10" s="57" t="s">
         <v>22</v>
       </c>
-      <c r="O10" s="59"/>
-      <c r="P10" s="60"/>
+      <c r="O10" s="60"/>
+      <c r="P10" s="61"/>
     </row>
     <row r="11" ht="28" customHeight="1" spans="1:16">
       <c r="A11" s="56">
@@ -2577,33 +2575,23 @@
       <c r="E11" s="57">
         <v>9.1</v>
       </c>
-      <c r="F11" s="57">
-        <v>9.5</v>
-      </c>
-      <c r="G11" s="57">
-        <v>9.6</v>
-      </c>
-      <c r="H11" s="57">
-        <v>9.11</v>
-      </c>
-      <c r="I11" s="57">
-        <v>9.12</v>
-      </c>
-      <c r="J11" s="57">
-        <v>9.18</v>
-      </c>
-      <c r="K11" s="57">
-        <v>9.19</v>
-      </c>
-      <c r="L11" s="57">
-        <v>9.25</v>
-      </c>
-      <c r="M11" s="57"/>
+      <c r="F11" s="57"/>
+      <c r="G11" s="57"/>
+      <c r="H11" s="57"/>
+      <c r="I11" s="57"/>
+      <c r="J11" s="57"/>
+      <c r="K11" s="57"/>
+      <c r="L11" s="62">
+        <v>46295</v>
+      </c>
+      <c r="M11" s="59">
+        <v>80</v>
+      </c>
       <c r="N11" s="57" t="s">
         <v>22</v>
       </c>
-      <c r="O11" s="59"/>
-      <c r="P11" s="60"/>
+      <c r="O11" s="60"/>
+      <c r="P11" s="61"/>
     </row>
     <row r="12" ht="28" customHeight="1" spans="1:16">
       <c r="A12" s="56">
@@ -2621,33 +2609,23 @@
       <c r="E12" s="57">
         <v>9.1</v>
       </c>
-      <c r="F12" s="57" t="s">
-        <v>33</v>
-      </c>
-      <c r="G12" s="57" t="s">
-        <v>33</v>
-      </c>
-      <c r="H12" s="57" t="s">
-        <v>33</v>
-      </c>
-      <c r="I12" s="57" t="s">
-        <v>33</v>
-      </c>
-      <c r="J12" s="57" t="s">
-        <v>33</v>
-      </c>
-      <c r="K12" s="57" t="s">
-        <v>33</v>
-      </c>
-      <c r="L12" s="57" t="s">
-        <v>33</v>
-      </c>
-      <c r="M12" s="57"/>
+      <c r="F12" s="57"/>
+      <c r="G12" s="57"/>
+      <c r="H12" s="57"/>
+      <c r="I12" s="57"/>
+      <c r="J12" s="57"/>
+      <c r="K12" s="57"/>
+      <c r="L12" s="62">
+        <v>46295</v>
+      </c>
+      <c r="M12" s="59">
+        <v>50</v>
+      </c>
       <c r="N12" s="57" t="s">
         <v>29</v>
       </c>
-      <c r="O12" s="59"/>
-      <c r="P12" s="60"/>
+      <c r="O12" s="60"/>
+      <c r="P12" s="61"/>
     </row>
     <row r="13" ht="28" customHeight="1" spans="1:16">
       <c r="A13" s="56">
@@ -2660,130 +2638,120 @@
         <v>27</v>
       </c>
       <c r="D13" s="58" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E13" s="57">
         <v>9.1</v>
       </c>
-      <c r="F13" s="57" t="s">
-        <v>33</v>
-      </c>
-      <c r="G13" s="57" t="s">
-        <v>33</v>
-      </c>
-      <c r="H13" s="57" t="s">
-        <v>33</v>
-      </c>
-      <c r="I13" s="57" t="s">
-        <v>33</v>
-      </c>
-      <c r="J13" s="57" t="s">
-        <v>33</v>
-      </c>
-      <c r="K13" s="57" t="s">
-        <v>33</v>
-      </c>
-      <c r="L13" s="57" t="s">
-        <v>33</v>
-      </c>
-      <c r="M13" s="57"/>
+      <c r="F13" s="57"/>
+      <c r="G13" s="57"/>
+      <c r="H13" s="57"/>
+      <c r="I13" s="57"/>
+      <c r="J13" s="57"/>
+      <c r="K13" s="57"/>
+      <c r="L13" s="62">
+        <v>46295</v>
+      </c>
+      <c r="M13" s="59">
+        <v>80</v>
+      </c>
       <c r="N13" s="57" t="s">
         <v>29</v>
       </c>
-      <c r="O13" s="59"/>
-      <c r="P13" s="60"/>
+      <c r="O13" s="60"/>
+      <c r="P13" s="61"/>
     </row>
     <row r="14" s="38" customFormat="1" ht="28" customHeight="1" spans="1:16">
       <c r="A14" s="56">
         <v>11</v>
       </c>
-      <c r="B14" s="61" t="s">
+      <c r="B14" s="63" t="s">
+        <v>34</v>
+      </c>
+      <c r="C14" s="63" t="s">
         <v>35</v>
       </c>
-      <c r="C14" s="61" t="s">
+      <c r="D14" s="60" t="s">
         <v>36</v>
       </c>
-      <c r="D14" s="59" t="s">
-        <v>37</v>
-      </c>
-      <c r="E14" s="62"/>
-      <c r="F14" s="62"/>
-      <c r="G14" s="62"/>
-      <c r="H14" s="62"/>
-      <c r="I14" s="62"/>
-      <c r="J14" s="62"/>
-      <c r="K14" s="62"/>
-      <c r="L14" s="62"/>
-      <c r="M14" s="62"/>
-      <c r="N14" s="62"/>
-      <c r="O14" s="59"/>
-      <c r="P14" s="60"/>
+      <c r="E14" s="64"/>
+      <c r="F14" s="64"/>
+      <c r="G14" s="64"/>
+      <c r="H14" s="64"/>
+      <c r="I14" s="64"/>
+      <c r="J14" s="64"/>
+      <c r="K14" s="64"/>
+      <c r="L14" s="64"/>
+      <c r="M14" s="64"/>
+      <c r="N14" s="64"/>
+      <c r="O14" s="60"/>
+      <c r="P14" s="61"/>
     </row>
     <row r="15" s="38" customFormat="1" ht="28" customHeight="1" spans="1:16">
       <c r="A15" s="56">
         <v>12</v>
       </c>
-      <c r="B15" s="63"/>
-      <c r="C15" s="63"/>
-      <c r="D15" s="59" t="s">
-        <v>38</v>
-      </c>
-      <c r="E15" s="62"/>
-      <c r="F15" s="62"/>
-      <c r="G15" s="62"/>
-      <c r="H15" s="62"/>
-      <c r="I15" s="62"/>
-      <c r="J15" s="62"/>
-      <c r="K15" s="62"/>
-      <c r="L15" s="62"/>
-      <c r="M15" s="62"/>
-      <c r="N15" s="62"/>
-      <c r="O15" s="59"/>
-      <c r="P15" s="60"/>
+      <c r="B15" s="65"/>
+      <c r="C15" s="65"/>
+      <c r="D15" s="60" t="s">
+        <v>37</v>
+      </c>
+      <c r="E15" s="64"/>
+      <c r="F15" s="64"/>
+      <c r="G15" s="64"/>
+      <c r="H15" s="64"/>
+      <c r="I15" s="64"/>
+      <c r="J15" s="64"/>
+      <c r="K15" s="64"/>
+      <c r="L15" s="64"/>
+      <c r="M15" s="64"/>
+      <c r="N15" s="64"/>
+      <c r="O15" s="60"/>
+      <c r="P15" s="61"/>
     </row>
     <row r="16" s="38" customFormat="1" ht="28" customHeight="1" spans="1:16">
       <c r="A16" s="56">
         <v>13</v>
       </c>
-      <c r="B16" s="64"/>
-      <c r="C16" s="64"/>
-      <c r="D16" s="59" t="s">
+      <c r="B16" s="66"/>
+      <c r="C16" s="66"/>
+      <c r="D16" s="60" t="s">
+        <v>38</v>
+      </c>
+      <c r="E16" s="64" t="s">
         <v>39</v>
       </c>
-      <c r="E16" s="62" t="s">
-        <v>33</v>
-      </c>
-      <c r="F16" s="62" t="s">
-        <v>33</v>
-      </c>
-      <c r="G16" s="62" t="s">
-        <v>33</v>
-      </c>
-      <c r="H16" s="62" t="s">
-        <v>33</v>
-      </c>
-      <c r="I16" s="62" t="s">
-        <v>33</v>
-      </c>
-      <c r="J16" s="62" t="s">
-        <v>33</v>
-      </c>
-      <c r="K16" s="62" t="s">
-        <v>33</v>
-      </c>
-      <c r="L16" s="62" t="s">
-        <v>33</v>
-      </c>
-      <c r="M16" s="62">
+      <c r="F16" s="64" t="s">
+        <v>39</v>
+      </c>
+      <c r="G16" s="64" t="s">
+        <v>39</v>
+      </c>
+      <c r="H16" s="64" t="s">
+        <v>39</v>
+      </c>
+      <c r="I16" s="64" t="s">
+        <v>39</v>
+      </c>
+      <c r="J16" s="64" t="s">
+        <v>39</v>
+      </c>
+      <c r="K16" s="64" t="s">
+        <v>39</v>
+      </c>
+      <c r="L16" s="64" t="s">
+        <v>39</v>
+      </c>
+      <c r="M16" s="64">
         <v>90</v>
       </c>
-      <c r="N16" s="62" t="s">
+      <c r="N16" s="64" t="s">
         <v>22</v>
       </c>
-      <c r="O16" s="59" t="s">
+      <c r="O16" s="60" t="s">
         <v>40</v>
       </c>
-      <c r="P16" s="60" t="s">
+      <c r="P16" s="61" t="s">
         <v>41</v>
       </c>
     </row>
@@ -2791,169 +2759,169 @@
       <c r="A17" s="56">
         <v>14</v>
       </c>
-      <c r="B17" s="61" t="s">
+      <c r="B17" s="63" t="s">
+        <v>34</v>
+      </c>
+      <c r="C17" s="63" t="s">
         <v>35</v>
       </c>
-      <c r="C17" s="61" t="s">
-        <v>36</v>
-      </c>
-      <c r="D17" s="59" t="s">
+      <c r="D17" s="60" t="s">
         <v>42</v>
       </c>
-      <c r="E17" s="62"/>
-      <c r="F17" s="62"/>
-      <c r="G17" s="62"/>
-      <c r="H17" s="62"/>
-      <c r="I17" s="62"/>
-      <c r="J17" s="62"/>
-      <c r="K17" s="62"/>
-      <c r="L17" s="62"/>
-      <c r="M17" s="62"/>
-      <c r="N17" s="62"/>
-      <c r="O17" s="59"/>
-      <c r="P17" s="60"/>
+      <c r="E17" s="64"/>
+      <c r="F17" s="64"/>
+      <c r="G17" s="64"/>
+      <c r="H17" s="64"/>
+      <c r="I17" s="64"/>
+      <c r="J17" s="64"/>
+      <c r="K17" s="64"/>
+      <c r="L17" s="64"/>
+      <c r="M17" s="64"/>
+      <c r="N17" s="64"/>
+      <c r="O17" s="60"/>
+      <c r="P17" s="61"/>
     </row>
     <row r="18" s="38" customFormat="1" ht="28" customHeight="1" spans="1:16">
       <c r="A18" s="56">
         <v>15</v>
       </c>
-      <c r="B18" s="63"/>
-      <c r="C18" s="63"/>
-      <c r="D18" s="59" t="s">
+      <c r="B18" s="65"/>
+      <c r="C18" s="65"/>
+      <c r="D18" s="60" t="s">
         <v>43</v>
       </c>
-      <c r="E18" s="62"/>
-      <c r="F18" s="62"/>
-      <c r="G18" s="62"/>
-      <c r="H18" s="62"/>
-      <c r="I18" s="62"/>
-      <c r="J18" s="62"/>
-      <c r="K18" s="62"/>
-      <c r="L18" s="62"/>
-      <c r="M18" s="62"/>
-      <c r="N18" s="62"/>
-      <c r="O18" s="59"/>
-      <c r="P18" s="60"/>
+      <c r="E18" s="64"/>
+      <c r="F18" s="64"/>
+      <c r="G18" s="64"/>
+      <c r="H18" s="64"/>
+      <c r="I18" s="64"/>
+      <c r="J18" s="64"/>
+      <c r="K18" s="64"/>
+      <c r="L18" s="64"/>
+      <c r="M18" s="64"/>
+      <c r="N18" s="64"/>
+      <c r="O18" s="60"/>
+      <c r="P18" s="61"/>
     </row>
     <row r="19" s="38" customFormat="1" ht="28" customHeight="1" spans="1:16">
       <c r="A19" s="56">
         <v>16</v>
       </c>
-      <c r="B19" s="63"/>
-      <c r="C19" s="63"/>
-      <c r="D19" s="59" t="s">
+      <c r="B19" s="65"/>
+      <c r="C19" s="65"/>
+      <c r="D19" s="60" t="s">
         <v>44</v>
       </c>
-      <c r="E19" s="62" t="s">
-        <v>33</v>
-      </c>
-      <c r="F19" s="62" t="s">
-        <v>33</v>
-      </c>
-      <c r="G19" s="62" t="s">
-        <v>33</v>
-      </c>
-      <c r="H19" s="62" t="s">
-        <v>33</v>
-      </c>
-      <c r="I19" s="62" t="s">
-        <v>33</v>
-      </c>
-      <c r="J19" s="62" t="s">
-        <v>33</v>
-      </c>
-      <c r="K19" s="62"/>
-      <c r="L19" s="62"/>
-      <c r="M19" s="62"/>
-      <c r="N19" s="62" t="s">
+      <c r="E19" s="64" t="s">
+        <v>39</v>
+      </c>
+      <c r="F19" s="64" t="s">
+        <v>39</v>
+      </c>
+      <c r="G19" s="64" t="s">
+        <v>39</v>
+      </c>
+      <c r="H19" s="64" t="s">
+        <v>39</v>
+      </c>
+      <c r="I19" s="64" t="s">
+        <v>39</v>
+      </c>
+      <c r="J19" s="64" t="s">
+        <v>39</v>
+      </c>
+      <c r="K19" s="64"/>
+      <c r="L19" s="64"/>
+      <c r="M19" s="64"/>
+      <c r="N19" s="64" t="s">
         <v>45</v>
       </c>
-      <c r="O19" s="59"/>
-      <c r="P19" s="60"/>
+      <c r="O19" s="60"/>
+      <c r="P19" s="61"/>
     </row>
     <row r="20" s="38" customFormat="1" ht="28" customHeight="1" spans="1:16">
       <c r="A20" s="56">
         <v>17</v>
       </c>
-      <c r="B20" s="63"/>
-      <c r="C20" s="63"/>
-      <c r="D20" s="59" t="s">
+      <c r="B20" s="65"/>
+      <c r="C20" s="65"/>
+      <c r="D20" s="60" t="s">
         <v>46</v>
       </c>
-      <c r="E20" s="62"/>
-      <c r="F20" s="62"/>
-      <c r="G20" s="62"/>
-      <c r="H20" s="62"/>
-      <c r="I20" s="62"/>
-      <c r="J20" s="62"/>
-      <c r="K20" s="62" t="s">
+      <c r="E20" s="64"/>
+      <c r="F20" s="64"/>
+      <c r="G20" s="64"/>
+      <c r="H20" s="64"/>
+      <c r="I20" s="64"/>
+      <c r="J20" s="64"/>
+      <c r="K20" s="64" t="s">
         <v>47</v>
       </c>
-      <c r="L20" s="62" t="s">
+      <c r="L20" s="64" t="s">
         <v>48</v>
       </c>
-      <c r="M20" s="62">
+      <c r="M20" s="64">
         <v>95</v>
       </c>
-      <c r="N20" s="62" t="s">
+      <c r="N20" s="64" t="s">
         <v>29</v>
       </c>
-      <c r="O20" s="59"/>
-      <c r="P20" s="60"/>
+      <c r="O20" s="60"/>
+      <c r="P20" s="61"/>
     </row>
     <row r="21" s="38" customFormat="1" ht="28" customHeight="1" spans="1:16">
       <c r="A21" s="56">
         <v>18</v>
       </c>
-      <c r="B21" s="61" t="s">
+      <c r="B21" s="63" t="s">
+        <v>34</v>
+      </c>
+      <c r="C21" s="63" t="s">
         <v>35</v>
       </c>
-      <c r="C21" s="61" t="s">
-        <v>36</v>
-      </c>
-      <c r="D21" s="59" t="s">
+      <c r="D21" s="60" t="s">
         <v>49</v>
       </c>
       <c r="E21" s="38"/>
-      <c r="F21" s="62"/>
-      <c r="G21" s="62"/>
-      <c r="H21" s="62"/>
-      <c r="I21" s="62"/>
-      <c r="J21" s="62"/>
-      <c r="K21" s="62"/>
-      <c r="L21" s="62"/>
-      <c r="M21" s="62"/>
-      <c r="N21" s="62"/>
-      <c r="O21" s="59"/>
-      <c r="P21" s="60"/>
+      <c r="F21" s="64"/>
+      <c r="G21" s="64"/>
+      <c r="H21" s="64"/>
+      <c r="I21" s="64"/>
+      <c r="J21" s="64"/>
+      <c r="K21" s="64"/>
+      <c r="L21" s="64"/>
+      <c r="M21" s="64"/>
+      <c r="N21" s="64"/>
+      <c r="O21" s="60"/>
+      <c r="P21" s="61"/>
     </row>
     <row r="22" s="38" customFormat="1" ht="28" customHeight="1" spans="1:16">
       <c r="A22" s="56">
         <v>19</v>
       </c>
-      <c r="B22" s="63"/>
-      <c r="C22" s="63"/>
-      <c r="D22" s="59" t="s">
+      <c r="B22" s="65"/>
+      <c r="C22" s="65"/>
+      <c r="D22" s="60" t="s">
         <v>50</v>
       </c>
-      <c r="E22" s="62" t="s">
+      <c r="E22" s="64" t="s">
         <v>51</v>
       </c>
-      <c r="F22" s="62" t="s">
+      <c r="F22" s="64" t="s">
         <v>52</v>
       </c>
-      <c r="G22" s="62"/>
-      <c r="H22" s="62"/>
-      <c r="I22" s="62"/>
-      <c r="J22" s="62"/>
-      <c r="K22" s="62"/>
-      <c r="L22" s="62"/>
-      <c r="M22" s="62"/>
-      <c r="N22" s="62"/>
-      <c r="O22" s="59" t="s">
+      <c r="G22" s="64"/>
+      <c r="H22" s="64"/>
+      <c r="I22" s="64"/>
+      <c r="J22" s="64"/>
+      <c r="K22" s="64"/>
+      <c r="L22" s="64"/>
+      <c r="M22" s="64"/>
+      <c r="N22" s="64"/>
+      <c r="O22" s="60" t="s">
         <v>40</v>
       </c>
-      <c r="P22" s="60" t="s">
+      <c r="P22" s="61" t="s">
         <v>41</v>
       </c>
     </row>
@@ -2961,683 +2929,683 @@
       <c r="A23" s="56">
         <v>20</v>
       </c>
-      <c r="B23" s="64"/>
-      <c r="C23" s="64"/>
-      <c r="D23" s="59" t="s">
+      <c r="B23" s="66"/>
+      <c r="C23" s="66"/>
+      <c r="D23" s="60" t="s">
         <v>53</v>
       </c>
-      <c r="E23" s="62"/>
-      <c r="F23" s="62"/>
-      <c r="G23" s="62" t="s">
-        <v>33</v>
-      </c>
-      <c r="H23" s="62" t="s">
-        <v>33</v>
-      </c>
-      <c r="I23" s="62" t="s">
-        <v>33</v>
-      </c>
-      <c r="J23" s="62" t="s">
-        <v>33</v>
-      </c>
-      <c r="K23" s="62" t="s">
-        <v>33</v>
-      </c>
-      <c r="L23" s="62" t="s">
-        <v>33</v>
-      </c>
-      <c r="M23" s="62">
+      <c r="E23" s="64"/>
+      <c r="F23" s="64"/>
+      <c r="G23" s="64" t="s">
+        <v>39</v>
+      </c>
+      <c r="H23" s="64" t="s">
+        <v>39</v>
+      </c>
+      <c r="I23" s="64" t="s">
+        <v>39</v>
+      </c>
+      <c r="J23" s="64" t="s">
+        <v>39</v>
+      </c>
+      <c r="K23" s="64" t="s">
+        <v>39</v>
+      </c>
+      <c r="L23" s="64" t="s">
+        <v>39</v>
+      </c>
+      <c r="M23" s="64">
         <v>80</v>
       </c>
-      <c r="N23" s="62" t="s">
+      <c r="N23" s="64" t="s">
         <v>22</v>
       </c>
-      <c r="O23" s="59"/>
-      <c r="P23" s="60"/>
+      <c r="O23" s="60"/>
+      <c r="P23" s="61"/>
     </row>
     <row r="24" s="38" customFormat="1" ht="28" customHeight="1" spans="1:16">
       <c r="A24" s="56">
         <v>21</v>
       </c>
-      <c r="B24" s="61" t="s">
+      <c r="B24" s="63" t="s">
+        <v>34</v>
+      </c>
+      <c r="C24" s="63" t="s">
         <v>35</v>
       </c>
-      <c r="C24" s="61" t="s">
-        <v>36</v>
-      </c>
-      <c r="D24" s="59" t="s">
+      <c r="D24" s="60" t="s">
         <v>54</v>
       </c>
-      <c r="E24" s="62"/>
-      <c r="F24" s="62"/>
-      <c r="G24" s="62"/>
-      <c r="H24" s="62"/>
-      <c r="I24" s="62"/>
-      <c r="J24" s="62"/>
-      <c r="K24" s="62"/>
-      <c r="L24" s="62"/>
-      <c r="M24" s="62"/>
-      <c r="N24" s="62"/>
-      <c r="O24" s="59"/>
-      <c r="P24" s="60"/>
+      <c r="E24" s="64"/>
+      <c r="F24" s="64"/>
+      <c r="G24" s="64"/>
+      <c r="H24" s="64"/>
+      <c r="I24" s="64"/>
+      <c r="J24" s="64"/>
+      <c r="K24" s="64"/>
+      <c r="L24" s="64"/>
+      <c r="M24" s="64"/>
+      <c r="N24" s="64"/>
+      <c r="O24" s="60"/>
+      <c r="P24" s="61"/>
     </row>
     <row r="25" s="38" customFormat="1" ht="28" customHeight="1" spans="1:16">
       <c r="A25" s="56">
         <v>22</v>
       </c>
-      <c r="B25" s="63"/>
-      <c r="C25" s="63"/>
-      <c r="D25" s="59" t="s">
+      <c r="B25" s="65"/>
+      <c r="C25" s="65"/>
+      <c r="D25" s="60" t="s">
         <v>55</v>
       </c>
-      <c r="E25" s="62" t="s">
+      <c r="E25" s="64" t="s">
         <v>51</v>
       </c>
-      <c r="F25" s="62" t="s">
+      <c r="F25" s="64" t="s">
         <v>56</v>
       </c>
       <c r="G25" s="38"/>
       <c r="H25" s="38"/>
-      <c r="I25" s="61"/>
-      <c r="J25" s="61"/>
-      <c r="K25" s="61"/>
-      <c r="L25" s="61"/>
-      <c r="M25" s="61"/>
-      <c r="N25" s="61" t="s">
+      <c r="I25" s="63"/>
+      <c r="J25" s="63"/>
+      <c r="K25" s="63"/>
+      <c r="L25" s="63"/>
+      <c r="M25" s="63"/>
+      <c r="N25" s="63" t="s">
         <v>22</v>
       </c>
-      <c r="O25" s="65" t="s">
+      <c r="O25" s="67" t="s">
         <v>40</v>
       </c>
-      <c r="P25" s="66"/>
+      <c r="P25" s="68"/>
     </row>
     <row r="26" s="38" customFormat="1" ht="28" customHeight="1" spans="1:16">
       <c r="A26" s="56">
         <v>23</v>
       </c>
-      <c r="B26" s="63"/>
-      <c r="C26" s="63"/>
-      <c r="D26" s="59" t="s">
+      <c r="B26" s="65"/>
+      <c r="C26" s="65"/>
+      <c r="D26" s="60" t="s">
         <v>57</v>
       </c>
-      <c r="E26" s="61"/>
-      <c r="F26" s="61"/>
-      <c r="G26" s="62" t="s">
-        <v>33</v>
-      </c>
-      <c r="H26" s="62" t="s">
-        <v>33</v>
-      </c>
-      <c r="I26" s="62" t="s">
-        <v>33</v>
-      </c>
-      <c r="J26" s="62" t="s">
-        <v>33</v>
-      </c>
-      <c r="K26" s="62" t="s">
-        <v>33</v>
-      </c>
-      <c r="L26" s="62" t="s">
-        <v>33</v>
-      </c>
-      <c r="M26" s="61">
+      <c r="E26" s="63"/>
+      <c r="F26" s="63"/>
+      <c r="G26" s="64" t="s">
+        <v>39</v>
+      </c>
+      <c r="H26" s="64" t="s">
+        <v>39</v>
+      </c>
+      <c r="I26" s="64" t="s">
+        <v>39</v>
+      </c>
+      <c r="J26" s="64" t="s">
+        <v>39</v>
+      </c>
+      <c r="K26" s="64" t="s">
+        <v>39</v>
+      </c>
+      <c r="L26" s="64" t="s">
+        <v>39</v>
+      </c>
+      <c r="M26" s="63">
         <v>90</v>
       </c>
-      <c r="N26" s="61"/>
-      <c r="O26" s="65"/>
-      <c r="P26" s="66"/>
+      <c r="N26" s="63"/>
+      <c r="O26" s="67"/>
+      <c r="P26" s="68"/>
     </row>
     <row r="27" s="38" customFormat="1" ht="28" customHeight="1" spans="1:16">
       <c r="A27" s="56">
         <v>24</v>
       </c>
-      <c r="B27" s="61" t="s">
+      <c r="B27" s="63" t="s">
+        <v>34</v>
+      </c>
+      <c r="C27" s="63" t="s">
         <v>35</v>
       </c>
-      <c r="C27" s="61" t="s">
-        <v>36</v>
-      </c>
-      <c r="D27" s="59" t="s">
+      <c r="D27" s="60" t="s">
         <v>58</v>
       </c>
-      <c r="E27" s="62"/>
-      <c r="F27" s="62"/>
-      <c r="G27" s="62"/>
-      <c r="H27" s="62"/>
-      <c r="I27" s="62"/>
-      <c r="J27" s="62"/>
-      <c r="K27" s="62"/>
-      <c r="L27" s="62"/>
-      <c r="M27" s="62"/>
-      <c r="N27" s="62" t="s">
+      <c r="E27" s="64"/>
+      <c r="F27" s="64"/>
+      <c r="G27" s="64"/>
+      <c r="H27" s="64"/>
+      <c r="I27" s="64"/>
+      <c r="J27" s="64"/>
+      <c r="K27" s="64"/>
+      <c r="L27" s="64"/>
+      <c r="M27" s="64"/>
+      <c r="N27" s="64" t="s">
         <v>59</v>
       </c>
-      <c r="O27" s="59"/>
-      <c r="P27" s="60"/>
+      <c r="O27" s="60"/>
+      <c r="P27" s="61"/>
     </row>
     <row r="28" s="39" customFormat="1" ht="28" customHeight="1" spans="1:16">
       <c r="A28" s="56">
         <v>25</v>
       </c>
-      <c r="B28" s="63"/>
-      <c r="C28" s="63"/>
-      <c r="D28" s="59" t="s">
+      <c r="B28" s="65"/>
+      <c r="C28" s="65"/>
+      <c r="D28" s="60" t="s">
         <v>60</v>
       </c>
-      <c r="E28" s="67"/>
-      <c r="F28" s="67"/>
-      <c r="G28" s="62"/>
-      <c r="H28" s="62"/>
-      <c r="I28" s="67"/>
-      <c r="J28" s="67"/>
-      <c r="K28" s="67"/>
-      <c r="L28" s="67"/>
-      <c r="M28" s="67"/>
-      <c r="N28" s="67" t="s">
+      <c r="E28" s="69"/>
+      <c r="F28" s="69"/>
+      <c r="G28" s="64"/>
+      <c r="H28" s="64"/>
+      <c r="I28" s="69"/>
+      <c r="J28" s="69"/>
+      <c r="K28" s="69"/>
+      <c r="L28" s="69"/>
+      <c r="M28" s="69"/>
+      <c r="N28" s="69" t="s">
         <v>59</v>
       </c>
-      <c r="O28" s="67"/>
-      <c r="P28" s="68"/>
+      <c r="O28" s="69"/>
+      <c r="P28" s="70"/>
     </row>
     <row r="29" s="39" customFormat="1" ht="28" customHeight="1" spans="1:16">
       <c r="A29" s="56">
         <v>26</v>
       </c>
-      <c r="B29" s="63"/>
-      <c r="C29" s="63"/>
-      <c r="D29" s="59" t="s">
+      <c r="B29" s="65"/>
+      <c r="C29" s="65"/>
+      <c r="D29" s="60" t="s">
         <v>61</v>
       </c>
-      <c r="E29" s="62" t="s">
-        <v>33</v>
-      </c>
-      <c r="F29" s="62" t="s">
-        <v>33</v>
-      </c>
-      <c r="G29" s="62" t="s">
-        <v>33</v>
-      </c>
-      <c r="H29" s="62" t="s">
-        <v>33</v>
-      </c>
-      <c r="I29" s="62" t="s">
-        <v>33</v>
-      </c>
-      <c r="J29" s="62" t="s">
-        <v>33</v>
-      </c>
-      <c r="K29" s="62"/>
-      <c r="L29" s="62"/>
-      <c r="M29" s="67">
+      <c r="E29" s="64" t="s">
+        <v>39</v>
+      </c>
+      <c r="F29" s="64" t="s">
+        <v>39</v>
+      </c>
+      <c r="G29" s="64" t="s">
+        <v>39</v>
+      </c>
+      <c r="H29" s="64" t="s">
+        <v>39</v>
+      </c>
+      <c r="I29" s="64" t="s">
+        <v>39</v>
+      </c>
+      <c r="J29" s="64" t="s">
+        <v>39</v>
+      </c>
+      <c r="K29" s="64"/>
+      <c r="L29" s="64"/>
+      <c r="M29" s="69">
         <v>95</v>
       </c>
-      <c r="N29" s="67" t="s">
+      <c r="N29" s="69" t="s">
         <v>22</v>
       </c>
-      <c r="O29" s="67"/>
-      <c r="P29" s="68"/>
+      <c r="O29" s="69"/>
+      <c r="P29" s="70"/>
     </row>
     <row r="30" s="39" customFormat="1" ht="28" customHeight="1" spans="1:16">
       <c r="A30" s="56">
         <v>27</v>
       </c>
-      <c r="B30" s="64"/>
-      <c r="C30" s="64"/>
-      <c r="D30" s="69" t="s">
+      <c r="B30" s="66"/>
+      <c r="C30" s="66"/>
+      <c r="D30" s="71" t="s">
         <v>62</v>
       </c>
-      <c r="E30" s="69"/>
-      <c r="F30" s="69"/>
-      <c r="G30" s="69"/>
-      <c r="H30" s="70"/>
-      <c r="I30" s="70"/>
-      <c r="J30" s="70"/>
-      <c r="K30" s="70" t="s">
+      <c r="E30" s="71"/>
+      <c r="F30" s="71"/>
+      <c r="G30" s="71"/>
+      <c r="H30" s="72"/>
+      <c r="I30" s="72"/>
+      <c r="J30" s="72"/>
+      <c r="K30" s="72" t="s">
         <v>47</v>
       </c>
-      <c r="L30" s="70" t="s">
+      <c r="L30" s="72" t="s">
         <v>48</v>
       </c>
-      <c r="M30" s="70">
+      <c r="M30" s="72">
         <v>100</v>
       </c>
-      <c r="N30" s="62"/>
-      <c r="O30" s="70" t="s">
+      <c r="N30" s="64"/>
+      <c r="O30" s="72" t="s">
         <v>63</v>
       </c>
-      <c r="P30" s="71"/>
+      <c r="P30" s="73"/>
     </row>
     <row r="31" s="39" customFormat="1" ht="28" customHeight="1" spans="1:16">
       <c r="A31" s="56">
         <v>28</v>
       </c>
-      <c r="B31" s="63" t="s">
+      <c r="B31" s="65" t="s">
+        <v>34</v>
+      </c>
+      <c r="C31" s="65" t="s">
         <v>35</v>
       </c>
-      <c r="C31" s="63" t="s">
-        <v>36</v>
-      </c>
-      <c r="D31" s="59" t="s">
+      <c r="D31" s="60" t="s">
         <v>64</v>
       </c>
-      <c r="E31" s="69" t="s">
+      <c r="E31" s="71" t="s">
         <v>51</v>
       </c>
-      <c r="F31" s="69" t="s">
+      <c r="F31" s="71" t="s">
         <v>52</v>
       </c>
-      <c r="G31" s="69"/>
-      <c r="H31" s="70"/>
-      <c r="I31" s="70"/>
-      <c r="J31" s="70"/>
-      <c r="K31" s="70"/>
-      <c r="L31" s="70"/>
-      <c r="M31" s="70"/>
-      <c r="N31" s="62"/>
-      <c r="O31" s="70"/>
-      <c r="P31" s="71"/>
+      <c r="G31" s="71"/>
+      <c r="H31" s="72"/>
+      <c r="I31" s="72"/>
+      <c r="J31" s="72"/>
+      <c r="K31" s="72"/>
+      <c r="L31" s="72"/>
+      <c r="M31" s="72"/>
+      <c r="N31" s="64"/>
+      <c r="O31" s="72"/>
+      <c r="P31" s="73"/>
     </row>
     <row r="32" s="39" customFormat="1" ht="28" customHeight="1" spans="1:16">
       <c r="A32" s="56">
         <v>29</v>
       </c>
-      <c r="B32" s="63"/>
-      <c r="C32" s="63"/>
-      <c r="D32" s="59" t="s">
+      <c r="B32" s="65"/>
+      <c r="C32" s="65"/>
+      <c r="D32" s="60" t="s">
         <v>65</v>
       </c>
-      <c r="E32" s="69"/>
-      <c r="F32" s="69"/>
-      <c r="G32" s="69"/>
-      <c r="H32" s="70" t="s">
+      <c r="E32" s="71"/>
+      <c r="F32" s="71"/>
+      <c r="G32" s="71"/>
+      <c r="H32" s="72" t="s">
         <v>66</v>
       </c>
-      <c r="I32" s="70"/>
-      <c r="J32" s="70"/>
-      <c r="K32" s="70"/>
-      <c r="L32" s="70"/>
-      <c r="M32" s="70"/>
-      <c r="N32" s="62"/>
-      <c r="O32" s="70"/>
-      <c r="P32" s="71"/>
+      <c r="I32" s="72"/>
+      <c r="J32" s="72"/>
+      <c r="K32" s="72"/>
+      <c r="L32" s="72"/>
+      <c r="M32" s="72"/>
+      <c r="N32" s="64"/>
+      <c r="O32" s="72"/>
+      <c r="P32" s="73"/>
     </row>
     <row r="33" s="39" customFormat="1" ht="28" customHeight="1" spans="1:16">
       <c r="A33" s="56">
         <v>30</v>
       </c>
-      <c r="B33" s="64"/>
-      <c r="C33" s="64"/>
-      <c r="D33" s="59" t="s">
+      <c r="B33" s="66"/>
+      <c r="C33" s="66"/>
+      <c r="D33" s="60" t="s">
         <v>67</v>
       </c>
-      <c r="E33" s="69"/>
-      <c r="F33" s="69"/>
-      <c r="G33" s="69"/>
-      <c r="H33" s="70"/>
-      <c r="I33" s="62" t="s">
-        <v>33</v>
-      </c>
-      <c r="J33" s="62" t="s">
-        <v>33</v>
-      </c>
-      <c r="K33" s="62" t="s">
-        <v>33</v>
-      </c>
-      <c r="L33" s="62" t="s">
-        <v>33</v>
-      </c>
-      <c r="M33" s="70">
+      <c r="E33" s="71"/>
+      <c r="F33" s="71"/>
+      <c r="G33" s="71"/>
+      <c r="H33" s="72"/>
+      <c r="I33" s="64" t="s">
+        <v>39</v>
+      </c>
+      <c r="J33" s="64" t="s">
+        <v>39</v>
+      </c>
+      <c r="K33" s="64" t="s">
+        <v>39</v>
+      </c>
+      <c r="L33" s="64" t="s">
+        <v>39</v>
+      </c>
+      <c r="M33" s="72">
         <v>50</v>
       </c>
-      <c r="N33" s="62" t="s">
+      <c r="N33" s="64" t="s">
         <v>29</v>
       </c>
-      <c r="O33" s="70"/>
-      <c r="P33" s="71"/>
+      <c r="O33" s="72"/>
+      <c r="P33" s="73"/>
     </row>
     <row r="34" s="39" customFormat="1" ht="28" customHeight="1" spans="1:16">
       <c r="A34" s="56">
         <v>31</v>
       </c>
-      <c r="B34" s="63" t="s">
+      <c r="B34" s="65" t="s">
         <v>19</v>
       </c>
-      <c r="C34" s="63" t="s">
-        <v>36</v>
-      </c>
-      <c r="D34" s="59" t="s">
+      <c r="C34" s="65" t="s">
+        <v>35</v>
+      </c>
+      <c r="D34" s="60" t="s">
         <v>68</v>
       </c>
-      <c r="E34" s="69" t="s">
+      <c r="E34" s="71" t="s">
         <v>51</v>
       </c>
-      <c r="F34" s="69" t="s">
+      <c r="F34" s="71" t="s">
         <v>52</v>
       </c>
-      <c r="G34" s="69"/>
-      <c r="H34" s="70"/>
-      <c r="I34" s="70"/>
-      <c r="J34" s="70"/>
-      <c r="K34" s="70"/>
-      <c r="L34" s="70"/>
-      <c r="M34" s="70"/>
-      <c r="N34" s="62"/>
-      <c r="O34" s="70"/>
-      <c r="P34" s="71"/>
+      <c r="G34" s="71"/>
+      <c r="H34" s="72"/>
+      <c r="I34" s="72"/>
+      <c r="J34" s="72"/>
+      <c r="K34" s="72"/>
+      <c r="L34" s="72"/>
+      <c r="M34" s="72"/>
+      <c r="N34" s="64"/>
+      <c r="O34" s="72"/>
+      <c r="P34" s="73"/>
     </row>
     <row r="35" s="39" customFormat="1" ht="28" customHeight="1" spans="1:16">
       <c r="A35" s="56">
         <v>32</v>
       </c>
-      <c r="B35" s="63"/>
-      <c r="C35" s="63"/>
-      <c r="D35" s="59" t="s">
+      <c r="B35" s="65"/>
+      <c r="C35" s="65"/>
+      <c r="D35" s="60" t="s">
         <v>69</v>
       </c>
-      <c r="E35" s="69"/>
-      <c r="F35" s="69"/>
+      <c r="E35" s="71"/>
+      <c r="F35" s="71"/>
       <c r="G35" s="39"/>
-      <c r="H35" s="70" t="s">
+      <c r="H35" s="72" t="s">
         <v>66</v>
       </c>
-      <c r="I35" s="70"/>
-      <c r="J35" s="70"/>
-      <c r="K35" s="70"/>
-      <c r="L35" s="70"/>
-      <c r="M35" s="70"/>
-      <c r="N35" s="62"/>
-      <c r="O35" s="70"/>
-      <c r="P35" s="71"/>
+      <c r="I35" s="72"/>
+      <c r="J35" s="72"/>
+      <c r="K35" s="72"/>
+      <c r="L35" s="72"/>
+      <c r="M35" s="72"/>
+      <c r="N35" s="64"/>
+      <c r="O35" s="72"/>
+      <c r="P35" s="73"/>
     </row>
     <row r="36" s="39" customFormat="1" ht="28" customHeight="1" spans="1:16">
       <c r="A36" s="56">
         <v>33</v>
       </c>
-      <c r="B36" s="64"/>
-      <c r="C36" s="64"/>
-      <c r="D36" s="59" t="s">
+      <c r="B36" s="66"/>
+      <c r="C36" s="66"/>
+      <c r="D36" s="60" t="s">
         <v>70</v>
       </c>
-      <c r="E36" s="69"/>
-      <c r="F36" s="69"/>
-      <c r="G36" s="69"/>
-      <c r="H36" s="70"/>
-      <c r="I36" s="62" t="s">
-        <v>33</v>
-      </c>
-      <c r="J36" s="62" t="s">
-        <v>33</v>
-      </c>
-      <c r="K36" s="62" t="s">
-        <v>33</v>
-      </c>
-      <c r="L36" s="62" t="s">
-        <v>33</v>
-      </c>
-      <c r="M36" s="70">
+      <c r="E36" s="71"/>
+      <c r="F36" s="71"/>
+      <c r="G36" s="71"/>
+      <c r="H36" s="72"/>
+      <c r="I36" s="64" t="s">
+        <v>39</v>
+      </c>
+      <c r="J36" s="64" t="s">
+        <v>39</v>
+      </c>
+      <c r="K36" s="64" t="s">
+        <v>39</v>
+      </c>
+      <c r="L36" s="64" t="s">
+        <v>39</v>
+      </c>
+      <c r="M36" s="72">
         <v>50</v>
       </c>
-      <c r="N36" s="62" t="s">
+      <c r="N36" s="64" t="s">
         <v>29</v>
       </c>
-      <c r="O36" s="70"/>
-      <c r="P36" s="71"/>
+      <c r="O36" s="72"/>
+      <c r="P36" s="73"/>
     </row>
     <row r="37" s="39" customFormat="1" ht="28" customHeight="1" spans="1:16">
       <c r="A37" s="56">
         <v>34</v>
       </c>
-      <c r="B37" s="72" t="s">
+      <c r="B37" s="74" t="s">
         <v>19</v>
       </c>
-      <c r="C37" s="72" t="s">
-        <v>36</v>
-      </c>
-      <c r="D37" s="59" t="s">
+      <c r="C37" s="74" t="s">
+        <v>35</v>
+      </c>
+      <c r="D37" s="60" t="s">
         <v>71</v>
       </c>
-      <c r="E37" s="69" t="s">
+      <c r="E37" s="71" t="s">
         <v>51</v>
       </c>
-      <c r="F37" s="69" t="s">
+      <c r="F37" s="71" t="s">
         <v>52</v>
       </c>
-      <c r="G37" s="69"/>
-      <c r="H37" s="70"/>
-      <c r="I37" s="70"/>
-      <c r="J37" s="70"/>
-      <c r="K37" s="70"/>
-      <c r="L37" s="70"/>
-      <c r="M37" s="70"/>
-      <c r="N37" s="62"/>
-      <c r="O37" s="70"/>
-      <c r="P37" s="71"/>
+      <c r="G37" s="71"/>
+      <c r="H37" s="72"/>
+      <c r="I37" s="72"/>
+      <c r="J37" s="72"/>
+      <c r="K37" s="72"/>
+      <c r="L37" s="72"/>
+      <c r="M37" s="72"/>
+      <c r="N37" s="64"/>
+      <c r="O37" s="72"/>
+      <c r="P37" s="73"/>
     </row>
     <row r="38" s="39" customFormat="1" ht="28" customHeight="1" spans="1:16">
       <c r="A38" s="56">
         <v>35</v>
       </c>
-      <c r="B38" s="72"/>
-      <c r="C38" s="72"/>
-      <c r="D38" s="59" t="s">
+      <c r="B38" s="74"/>
+      <c r="C38" s="74"/>
+      <c r="D38" s="60" t="s">
         <v>72</v>
       </c>
-      <c r="E38" s="69"/>
-      <c r="F38" s="69"/>
+      <c r="E38" s="71"/>
+      <c r="F38" s="71"/>
       <c r="G38" s="39"/>
-      <c r="H38" s="70" t="s">
+      <c r="H38" s="72" t="s">
         <v>66</v>
       </c>
-      <c r="I38" s="70"/>
-      <c r="J38" s="70"/>
-      <c r="K38" s="70"/>
-      <c r="L38" s="70"/>
-      <c r="M38" s="70"/>
-      <c r="N38" s="62"/>
-      <c r="O38" s="70"/>
-      <c r="P38" s="71"/>
+      <c r="I38" s="72"/>
+      <c r="J38" s="72"/>
+      <c r="K38" s="72"/>
+      <c r="L38" s="72"/>
+      <c r="M38" s="72"/>
+      <c r="N38" s="64"/>
+      <c r="O38" s="72"/>
+      <c r="P38" s="73"/>
     </row>
     <row r="39" s="39" customFormat="1" ht="28" customHeight="1" spans="1:16">
       <c r="A39" s="56">
         <v>36</v>
       </c>
-      <c r="B39" s="73"/>
-      <c r="C39" s="73"/>
-      <c r="D39" s="59" t="s">
+      <c r="B39" s="75"/>
+      <c r="C39" s="75"/>
+      <c r="D39" s="60" t="s">
         <v>73</v>
       </c>
-      <c r="E39" s="69"/>
-      <c r="F39" s="69"/>
-      <c r="G39" s="69"/>
-      <c r="H39" s="70"/>
-      <c r="I39" s="62" t="s">
-        <v>33</v>
-      </c>
-      <c r="J39" s="62" t="s">
-        <v>33</v>
-      </c>
-      <c r="K39" s="62" t="s">
-        <v>33</v>
-      </c>
-      <c r="L39" s="62" t="s">
-        <v>33</v>
-      </c>
-      <c r="M39" s="70">
+      <c r="E39" s="71"/>
+      <c r="F39" s="71"/>
+      <c r="G39" s="71"/>
+      <c r="H39" s="72"/>
+      <c r="I39" s="64" t="s">
+        <v>39</v>
+      </c>
+      <c r="J39" s="64" t="s">
+        <v>39</v>
+      </c>
+      <c r="K39" s="64" t="s">
+        <v>39</v>
+      </c>
+      <c r="L39" s="64" t="s">
+        <v>39</v>
+      </c>
+      <c r="M39" s="72">
         <v>50</v>
       </c>
-      <c r="N39" s="62" t="s">
+      <c r="N39" s="64" t="s">
         <v>29</v>
       </c>
-      <c r="O39" s="70"/>
-      <c r="P39" s="71"/>
+      <c r="O39" s="72"/>
+      <c r="P39" s="73"/>
     </row>
     <row r="40" s="40" customFormat="1" ht="28" customHeight="1" spans="1:16">
       <c r="A40" s="56">
         <v>37</v>
       </c>
-      <c r="B40" s="69" t="s">
+      <c r="B40" s="71" t="s">
         <v>19</v>
       </c>
-      <c r="C40" s="69" t="s">
+      <c r="C40" s="71" t="s">
         <v>27</v>
       </c>
-      <c r="D40" s="69" t="s">
+      <c r="D40" s="71" t="s">
         <v>74</v>
       </c>
-      <c r="E40" s="69"/>
-      <c r="F40" s="69"/>
-      <c r="G40" s="69"/>
-      <c r="H40" s="70"/>
-      <c r="I40" s="70"/>
-      <c r="J40" s="70"/>
-      <c r="K40" s="70"/>
-      <c r="L40" s="70"/>
-      <c r="M40" s="70"/>
-      <c r="N40" s="62" t="s">
+      <c r="E40" s="71"/>
+      <c r="F40" s="71"/>
+      <c r="G40" s="71"/>
+      <c r="H40" s="72"/>
+      <c r="I40" s="72"/>
+      <c r="J40" s="72"/>
+      <c r="K40" s="72"/>
+      <c r="L40" s="72"/>
+      <c r="M40" s="72"/>
+      <c r="N40" s="64" t="s">
         <v>59</v>
       </c>
-      <c r="O40" s="70" t="s">
+      <c r="O40" s="72" t="s">
         <v>75</v>
       </c>
-      <c r="P40" s="71"/>
+      <c r="P40" s="73"/>
     </row>
     <row r="41" s="40" customFormat="1" ht="19" customHeight="1" spans="1:16">
       <c r="A41" s="56">
         <v>38</v>
       </c>
-      <c r="B41" s="70" t="s">
+      <c r="B41" s="72" t="s">
         <v>19</v>
       </c>
-      <c r="C41" s="70" t="s">
+      <c r="C41" s="72" t="s">
         <v>27</v>
       </c>
-      <c r="D41" s="69" t="s">
+      <c r="D41" s="71" t="s">
         <v>76</v>
       </c>
-      <c r="E41" s="62" t="s">
-        <v>33</v>
-      </c>
-      <c r="F41" s="62" t="s">
-        <v>33</v>
-      </c>
-      <c r="G41" s="62" t="s">
-        <v>33</v>
-      </c>
-      <c r="H41" s="62" t="s">
-        <v>33</v>
-      </c>
-      <c r="I41" s="62" t="s">
-        <v>33</v>
-      </c>
-      <c r="J41" s="62" t="s">
-        <v>33</v>
-      </c>
-      <c r="K41" s="62" t="s">
-        <v>33</v>
-      </c>
-      <c r="L41" s="70" t="s">
+      <c r="E41" s="64" t="s">
+        <v>39</v>
+      </c>
+      <c r="F41" s="64" t="s">
+        <v>39</v>
+      </c>
+      <c r="G41" s="64" t="s">
+        <v>39</v>
+      </c>
+      <c r="H41" s="64" t="s">
+        <v>39</v>
+      </c>
+      <c r="I41" s="64" t="s">
+        <v>39</v>
+      </c>
+      <c r="J41" s="64" t="s">
+        <v>39</v>
+      </c>
+      <c r="K41" s="64" t="s">
+        <v>39</v>
+      </c>
+      <c r="L41" s="72" t="s">
         <v>48</v>
       </c>
-      <c r="M41" s="70">
+      <c r="M41" s="72">
         <v>100</v>
       </c>
-      <c r="N41" s="62" t="s">
+      <c r="N41" s="64" t="s">
         <v>22</v>
       </c>
-      <c r="O41" s="70" t="s">
+      <c r="O41" s="72" t="s">
         <v>75</v>
       </c>
-      <c r="P41" s="71"/>
+      <c r="P41" s="73"/>
     </row>
     <row r="42" s="40" customFormat="1" ht="19" customHeight="1" spans="1:16">
       <c r="A42" s="56">
         <v>39</v>
       </c>
-      <c r="B42" s="70" t="s">
+      <c r="B42" s="72" t="s">
         <v>19</v>
       </c>
-      <c r="C42" s="70" t="s">
+      <c r="C42" s="72" t="s">
         <v>27</v>
       </c>
-      <c r="D42" s="74" t="s">
+      <c r="D42" s="76" t="s">
         <v>77</v>
       </c>
-      <c r="E42" s="70"/>
-      <c r="F42" s="70"/>
-      <c r="G42" s="70"/>
-      <c r="H42" s="70"/>
-      <c r="I42" s="70"/>
-      <c r="J42" s="70"/>
-      <c r="K42" s="70"/>
-      <c r="L42" s="70"/>
-      <c r="M42" s="70"/>
-      <c r="N42" s="62" t="s">
+      <c r="E42" s="72"/>
+      <c r="F42" s="72"/>
+      <c r="G42" s="72"/>
+      <c r="H42" s="72"/>
+      <c r="I42" s="72"/>
+      <c r="J42" s="72"/>
+      <c r="K42" s="72"/>
+      <c r="L42" s="72"/>
+      <c r="M42" s="72"/>
+      <c r="N42" s="64" t="s">
         <v>59</v>
       </c>
-      <c r="O42" s="70" t="s">
+      <c r="O42" s="72" t="s">
         <v>75</v>
       </c>
-      <c r="P42" s="71"/>
+      <c r="P42" s="73"/>
     </row>
     <row r="43" s="40" customFormat="1" ht="19" customHeight="1" spans="1:16">
       <c r="A43" s="56">
         <v>40</v>
       </c>
-      <c r="B43" s="70" t="s">
+      <c r="B43" s="72" t="s">
         <v>19</v>
       </c>
-      <c r="C43" s="70" t="s">
+      <c r="C43" s="72" t="s">
         <v>27</v>
       </c>
-      <c r="D43" s="74" t="s">
+      <c r="D43" s="76" t="s">
         <v>78</v>
       </c>
-      <c r="E43" s="70"/>
-      <c r="F43" s="70"/>
-      <c r="G43" s="75"/>
-      <c r="H43" s="70"/>
-      <c r="I43" s="70"/>
-      <c r="J43" s="70"/>
-      <c r="K43" s="70"/>
-      <c r="L43" s="70"/>
-      <c r="M43" s="70"/>
-      <c r="N43" s="62" t="s">
+      <c r="E43" s="72"/>
+      <c r="F43" s="72"/>
+      <c r="G43" s="77"/>
+      <c r="H43" s="72"/>
+      <c r="I43" s="72"/>
+      <c r="J43" s="72"/>
+      <c r="K43" s="72"/>
+      <c r="L43" s="72"/>
+      <c r="M43" s="72"/>
+      <c r="N43" s="64" t="s">
         <v>59</v>
       </c>
-      <c r="O43" s="70" t="s">
+      <c r="O43" s="72" t="s">
         <v>75</v>
       </c>
-      <c r="P43" s="71"/>
+      <c r="P43" s="73"/>
     </row>
     <row r="44" s="40" customFormat="1" ht="19" customHeight="1" spans="1:16">
       <c r="A44" s="56">
         <v>41</v>
       </c>
-      <c r="B44" s="70" t="s">
+      <c r="B44" s="72" t="s">
         <v>19</v>
       </c>
-      <c r="C44" s="70" t="s">
+      <c r="C44" s="72" t="s">
         <v>27</v>
       </c>
-      <c r="D44" s="74" t="s">
+      <c r="D44" s="76" t="s">
         <v>79</v>
       </c>
-      <c r="E44" s="62"/>
-      <c r="F44" s="62"/>
-      <c r="G44" s="62"/>
-      <c r="H44" s="62"/>
-      <c r="I44" s="70"/>
-      <c r="J44" s="70"/>
-      <c r="K44" s="70"/>
-      <c r="L44" s="70"/>
-      <c r="M44" s="70"/>
-      <c r="N44" s="62" t="s">
+      <c r="E44" s="64"/>
+      <c r="F44" s="64"/>
+      <c r="G44" s="64"/>
+      <c r="H44" s="64"/>
+      <c r="I44" s="72"/>
+      <c r="J44" s="72"/>
+      <c r="K44" s="72"/>
+      <c r="L44" s="72"/>
+      <c r="M44" s="72"/>
+      <c r="N44" s="64" t="s">
         <v>29</v>
       </c>
-      <c r="O44" s="70" t="s">
+      <c r="O44" s="72" t="s">
         <v>63</v>
       </c>
-      <c r="P44" s="71" t="s">
+      <c r="P44" s="73" t="s">
         <v>80</v>
       </c>
     </row>
@@ -3645,133 +3613,133 @@
       <c r="A45" s="56">
         <v>42</v>
       </c>
-      <c r="B45" s="76" t="s">
+      <c r="B45" s="78" t="s">
         <v>19</v>
       </c>
-      <c r="C45" s="76" t="s">
+      <c r="C45" s="78" t="s">
         <v>27</v>
       </c>
-      <c r="D45" s="77" t="s">
+      <c r="D45" s="79" t="s">
         <v>81</v>
       </c>
-      <c r="E45" s="62" t="s">
-        <v>33</v>
-      </c>
-      <c r="F45" s="62" t="s">
-        <v>33</v>
-      </c>
-      <c r="G45" s="62" t="s">
-        <v>33</v>
-      </c>
-      <c r="H45" s="62" t="s">
-        <v>33</v>
-      </c>
-      <c r="I45" s="62" t="s">
-        <v>33</v>
-      </c>
-      <c r="J45" s="62" t="s">
-        <v>33</v>
-      </c>
-      <c r="K45" s="62" t="s">
-        <v>33</v>
-      </c>
-      <c r="L45" s="76" t="s">
+      <c r="E45" s="64" t="s">
+        <v>39</v>
+      </c>
+      <c r="F45" s="64" t="s">
+        <v>39</v>
+      </c>
+      <c r="G45" s="64" t="s">
+        <v>39</v>
+      </c>
+      <c r="H45" s="64" t="s">
+        <v>39</v>
+      </c>
+      <c r="I45" s="64" t="s">
+        <v>39</v>
+      </c>
+      <c r="J45" s="64" t="s">
+        <v>39</v>
+      </c>
+      <c r="K45" s="64" t="s">
+        <v>39</v>
+      </c>
+      <c r="L45" s="78" t="s">
         <v>48</v>
       </c>
-      <c r="M45" s="76">
+      <c r="M45" s="78">
         <v>95</v>
       </c>
-      <c r="N45" s="61" t="s">
+      <c r="N45" s="63" t="s">
         <v>22</v>
       </c>
-      <c r="O45" s="70" t="s">
+      <c r="O45" s="72" t="s">
         <v>75</v>
       </c>
-      <c r="P45" s="78"/>
+      <c r="P45" s="80"/>
     </row>
     <row r="46" s="40" customFormat="1" ht="19" customHeight="1" spans="1:16">
       <c r="A46" s="56">
         <v>43</v>
       </c>
-      <c r="B46" s="76" t="s">
+      <c r="B46" s="78" t="s">
         <v>19</v>
       </c>
-      <c r="C46" s="76" t="s">
+      <c r="C46" s="78" t="s">
         <v>27</v>
       </c>
-      <c r="D46" s="76" t="s">
+      <c r="D46" s="78" t="s">
         <v>82</v>
       </c>
-      <c r="E46" s="62" t="s">
-        <v>33</v>
-      </c>
-      <c r="F46" s="62" t="s">
-        <v>33</v>
-      </c>
-      <c r="G46" s="62" t="s">
-        <v>33</v>
-      </c>
-      <c r="H46" s="62" t="s">
-        <v>33</v>
-      </c>
-      <c r="I46" s="62" t="s">
-        <v>33</v>
-      </c>
-      <c r="J46" s="62" t="s">
-        <v>33</v>
-      </c>
-      <c r="K46" s="62" t="s">
-        <v>33</v>
-      </c>
-      <c r="L46" s="76" t="s">
+      <c r="E46" s="64" t="s">
+        <v>39</v>
+      </c>
+      <c r="F46" s="64" t="s">
+        <v>39</v>
+      </c>
+      <c r="G46" s="64" t="s">
+        <v>39</v>
+      </c>
+      <c r="H46" s="64" t="s">
+        <v>39</v>
+      </c>
+      <c r="I46" s="64" t="s">
+        <v>39</v>
+      </c>
+      <c r="J46" s="64" t="s">
+        <v>39</v>
+      </c>
+      <c r="K46" s="64" t="s">
+        <v>39</v>
+      </c>
+      <c r="L46" s="78" t="s">
         <v>48</v>
       </c>
-      <c r="M46" s="76">
+      <c r="M46" s="78">
         <v>90</v>
       </c>
-      <c r="N46" s="61" t="s">
+      <c r="N46" s="63" t="s">
         <v>22</v>
       </c>
-      <c r="O46" s="70" t="s">
+      <c r="O46" s="72" t="s">
         <v>75</v>
       </c>
-      <c r="P46" s="78"/>
+      <c r="P46" s="80"/>
     </row>
     <row r="47" s="40" customFormat="1" ht="19" customHeight="1" spans="1:16">
       <c r="A47" s="56">
         <v>44</v>
       </c>
-      <c r="B47" s="76" t="s">
+      <c r="B47" s="78" t="s">
         <v>19</v>
       </c>
-      <c r="C47" s="76" t="s">
+      <c r="C47" s="78" t="s">
         <v>27</v>
       </c>
-      <c r="D47" s="76" t="s">
+      <c r="D47" s="78" t="s">
         <v>83</v>
       </c>
-      <c r="E47" s="62"/>
-      <c r="F47" s="62"/>
-      <c r="G47" s="62"/>
-      <c r="H47" s="62"/>
-      <c r="I47" s="62"/>
-      <c r="J47" s="62"/>
-      <c r="K47" s="62" t="s">
+      <c r="E47" s="64"/>
+      <c r="F47" s="64"/>
+      <c r="G47" s="64"/>
+      <c r="H47" s="64"/>
+      <c r="I47" s="64"/>
+      <c r="J47" s="64"/>
+      <c r="K47" s="64" t="s">
         <v>47</v>
       </c>
-      <c r="L47" s="62" t="s">
+      <c r="L47" s="64" t="s">
         <v>48</v>
       </c>
-      <c r="M47" s="76">
+      <c r="M47" s="78">
         <v>50</v>
       </c>
-      <c r="N47" s="61" t="s">
+      <c r="N47" s="63" t="s">
         <v>22</v>
       </c>
-      <c r="O47" s="70" t="s">
+      <c r="O47" s="72" t="s">
         <v>75</v>
       </c>
-      <c r="P47" s="60" t="s">
+      <c r="P47" s="61" t="s">
         <v>84</v>
       </c>
     </row>
@@ -3779,37 +3747,37 @@
       <c r="A48" s="56">
         <v>45</v>
       </c>
-      <c r="B48" s="76" t="s">
+      <c r="B48" s="78" t="s">
         <v>19</v>
       </c>
-      <c r="C48" s="76" t="s">
+      <c r="C48" s="78" t="s">
         <v>27</v>
       </c>
-      <c r="D48" s="76" t="s">
+      <c r="D48" s="78" t="s">
         <v>83</v>
       </c>
-      <c r="E48" s="62"/>
-      <c r="F48" s="62"/>
-      <c r="G48" s="62"/>
-      <c r="H48" s="62"/>
-      <c r="I48" s="62"/>
-      <c r="J48" s="62"/>
-      <c r="K48" s="62" t="s">
+      <c r="E48" s="64"/>
+      <c r="F48" s="64"/>
+      <c r="G48" s="64"/>
+      <c r="H48" s="64"/>
+      <c r="I48" s="64"/>
+      <c r="J48" s="64"/>
+      <c r="K48" s="64" t="s">
         <v>47</v>
       </c>
-      <c r="L48" s="62" t="s">
+      <c r="L48" s="64" t="s">
         <v>48</v>
       </c>
-      <c r="M48" s="76">
+      <c r="M48" s="78">
         <v>50</v>
       </c>
-      <c r="N48" s="61" t="s">
+      <c r="N48" s="63" t="s">
         <v>22</v>
       </c>
-      <c r="O48" s="70" t="s">
+      <c r="O48" s="72" t="s">
         <v>75</v>
       </c>
-      <c r="P48" s="60" t="s">
+      <c r="P48" s="61" t="s">
         <v>84</v>
       </c>
     </row>
@@ -3817,229 +3785,229 @@
       <c r="A49" s="56">
         <v>46</v>
       </c>
-      <c r="B49" s="79" t="s">
+      <c r="B49" s="81" t="s">
         <v>85</v>
       </c>
-      <c r="C49" s="79"/>
-      <c r="D49" s="79"/>
-      <c r="E49" s="79"/>
-      <c r="F49" s="79"/>
-      <c r="G49" s="79"/>
-      <c r="H49" s="79"/>
-      <c r="I49" s="79"/>
-      <c r="J49" s="79"/>
-      <c r="K49" s="79"/>
-      <c r="L49" s="79"/>
-      <c r="M49" s="79"/>
-      <c r="N49" s="79"/>
-      <c r="O49" s="79"/>
-      <c r="P49" s="80"/>
+      <c r="C49" s="81"/>
+      <c r="D49" s="81"/>
+      <c r="E49" s="81"/>
+      <c r="F49" s="81"/>
+      <c r="G49" s="81"/>
+      <c r="H49" s="81"/>
+      <c r="I49" s="81"/>
+      <c r="J49" s="81"/>
+      <c r="K49" s="81"/>
+      <c r="L49" s="81"/>
+      <c r="M49" s="81"/>
+      <c r="N49" s="81"/>
+      <c r="O49" s="81"/>
+      <c r="P49" s="82"/>
     </row>
     <row r="50" ht="32" customHeight="1" spans="1:16">
-      <c r="A50" s="81" t="s">
+      <c r="A50" s="83" t="s">
         <v>86</v>
       </c>
-      <c r="B50" s="82"/>
-      <c r="C50" s="82"/>
-      <c r="D50" s="82"/>
-      <c r="E50" s="82"/>
-      <c r="F50" s="82"/>
-      <c r="G50" s="82"/>
-      <c r="H50" s="82"/>
-      <c r="I50" s="82"/>
-      <c r="J50" s="82"/>
+      <c r="B50" s="84"/>
+      <c r="C50" s="84"/>
+      <c r="D50" s="84"/>
+      <c r="E50" s="84"/>
+      <c r="F50" s="84"/>
+      <c r="G50" s="84"/>
+      <c r="H50" s="84"/>
+      <c r="I50" s="84"/>
+      <c r="J50" s="84"/>
     </row>
     <row r="51" ht="32" customHeight="1" spans="1:16">
-      <c r="A51" s="83" t="s">
+      <c r="A51" s="85" t="s">
         <v>9</v>
       </c>
-      <c r="B51" s="83" t="s">
+      <c r="B51" s="85" t="s">
         <v>10</v>
       </c>
-      <c r="C51" s="83" t="s">
+      <c r="C51" s="85" t="s">
         <v>11</v>
       </c>
-      <c r="D51" s="83" t="s">
+      <c r="D51" s="85" t="s">
         <v>87</v>
       </c>
-      <c r="E51" s="84" t="s">
+      <c r="E51" s="86" t="s">
         <v>88</v>
       </c>
-      <c r="F51" s="85"/>
-      <c r="G51" s="86"/>
-      <c r="H51" s="84" t="s">
+      <c r="F51" s="87"/>
+      <c r="G51" s="88"/>
+      <c r="H51" s="86" t="s">
         <v>89</v>
       </c>
-      <c r="I51" s="85"/>
-      <c r="J51" s="86"/>
+      <c r="I51" s="87"/>
+      <c r="J51" s="88"/>
     </row>
     <row r="52" ht="32" customHeight="1" spans="1:16">
-      <c r="A52" s="87">
+      <c r="A52" s="89">
         <v>1</v>
       </c>
-      <c r="B52" s="88" t="s">
+      <c r="B52" s="90" t="s">
         <v>19</v>
       </c>
-      <c r="C52" s="88" t="s">
+      <c r="C52" s="90" t="s">
         <v>27</v>
       </c>
-      <c r="D52" s="88" t="s">
+      <c r="D52" s="90" t="s">
         <v>90</v>
       </c>
-      <c r="E52" s="89" t="s">
+      <c r="E52" s="91" t="s">
         <v>40</v>
       </c>
-      <c r="F52" s="90"/>
-      <c r="G52" s="91"/>
-      <c r="H52" s="89"/>
-      <c r="I52" s="90"/>
-      <c r="J52" s="91"/>
+      <c r="F52" s="92"/>
+      <c r="G52" s="93"/>
+      <c r="H52" s="91"/>
+      <c r="I52" s="92"/>
+      <c r="J52" s="93"/>
     </row>
     <row r="53" ht="32" customHeight="1" spans="1:16">
-      <c r="A53" s="87">
+      <c r="A53" s="89">
         <v>2</v>
       </c>
-      <c r="B53" s="88" t="s">
+      <c r="B53" s="90" t="s">
         <v>19</v>
       </c>
-      <c r="C53" s="88" t="s">
+      <c r="C53" s="90" t="s">
         <v>27</v>
       </c>
-      <c r="D53" s="88" t="s">
+      <c r="D53" s="90" t="s">
         <v>91</v>
       </c>
-      <c r="E53" s="89" t="s">
+      <c r="E53" s="91" t="s">
         <v>40</v>
       </c>
-      <c r="F53" s="90"/>
-      <c r="G53" s="91"/>
-      <c r="H53" s="89"/>
-      <c r="I53" s="90"/>
-      <c r="J53" s="91"/>
+      <c r="F53" s="92"/>
+      <c r="G53" s="93"/>
+      <c r="H53" s="91"/>
+      <c r="I53" s="92"/>
+      <c r="J53" s="93"/>
     </row>
     <row r="54" ht="32" customHeight="1" spans="1:16">
-      <c r="A54" s="87">
+      <c r="A54" s="89">
         <v>3</v>
       </c>
-      <c r="B54" s="87" t="s">
+      <c r="B54" s="89" t="s">
         <v>19</v>
       </c>
-      <c r="C54" s="87"/>
-      <c r="D54" s="87"/>
-      <c r="E54" s="92"/>
-      <c r="F54" s="93"/>
-      <c r="G54" s="94"/>
-      <c r="H54" s="92"/>
-      <c r="I54" s="93"/>
-      <c r="J54" s="94"/>
+      <c r="C54" s="89"/>
+      <c r="D54" s="89"/>
+      <c r="E54" s="94"/>
+      <c r="F54" s="95"/>
+      <c r="G54" s="96"/>
+      <c r="H54" s="94"/>
+      <c r="I54" s="95"/>
+      <c r="J54" s="96"/>
     </row>
     <row r="55" ht="32" customHeight="1" spans="1:16">
-      <c r="A55" s="87">
+      <c r="A55" s="89">
         <v>4</v>
       </c>
-      <c r="B55" s="87" t="s">
+      <c r="B55" s="89" t="s">
         <v>19</v>
       </c>
-      <c r="C55" s="87"/>
-      <c r="D55" s="87"/>
-      <c r="E55" s="92"/>
-      <c r="F55" s="93"/>
-      <c r="G55" s="94"/>
-      <c r="H55" s="92"/>
-      <c r="I55" s="93"/>
-      <c r="J55" s="94"/>
+      <c r="C55" s="89"/>
+      <c r="D55" s="89"/>
+      <c r="E55" s="94"/>
+      <c r="F55" s="95"/>
+      <c r="G55" s="96"/>
+      <c r="H55" s="94"/>
+      <c r="I55" s="95"/>
+      <c r="J55" s="96"/>
     </row>
     <row r="56" ht="32" customHeight="1" spans="1:16">
-      <c r="A56" s="87">
+      <c r="A56" s="89">
         <v>5</v>
       </c>
-      <c r="B56" s="87" t="s">
+      <c r="B56" s="89" t="s">
         <v>92</v>
       </c>
-      <c r="C56" s="87"/>
-      <c r="D56" s="87"/>
-      <c r="E56" s="92"/>
-      <c r="F56" s="93"/>
-      <c r="G56" s="94"/>
-      <c r="H56" s="92"/>
-      <c r="I56" s="93"/>
-      <c r="J56" s="94"/>
+      <c r="C56" s="89"/>
+      <c r="D56" s="89"/>
+      <c r="E56" s="94"/>
+      <c r="F56" s="95"/>
+      <c r="G56" s="96"/>
+      <c r="H56" s="94"/>
+      <c r="I56" s="95"/>
+      <c r="J56" s="96"/>
     </row>
     <row r="57" ht="32" customHeight="1" spans="1:16">
-      <c r="A57" s="87">
+      <c r="A57" s="89">
         <v>6</v>
       </c>
-      <c r="B57" s="87" t="s">
+      <c r="B57" s="89" t="s">
         <v>19</v>
       </c>
-      <c r="C57" s="87"/>
-      <c r="D57" s="87"/>
-      <c r="E57" s="92"/>
-      <c r="F57" s="93"/>
-      <c r="G57" s="94"/>
-      <c r="H57" s="92"/>
-      <c r="I57" s="93"/>
-      <c r="J57" s="94"/>
+      <c r="C57" s="89"/>
+      <c r="D57" s="89"/>
+      <c r="E57" s="94"/>
+      <c r="F57" s="95"/>
+      <c r="G57" s="96"/>
+      <c r="H57" s="94"/>
+      <c r="I57" s="95"/>
+      <c r="J57" s="96"/>
     </row>
     <row r="58" ht="32" customHeight="1" spans="1:16">
-      <c r="A58" s="87"/>
-      <c r="B58" s="87"/>
-      <c r="C58" s="87"/>
-      <c r="D58" s="87"/>
-      <c r="E58" s="92"/>
-      <c r="F58" s="93"/>
-      <c r="G58" s="94"/>
-      <c r="H58" s="92"/>
-      <c r="I58" s="93"/>
-      <c r="J58" s="94"/>
+      <c r="A58" s="89"/>
+      <c r="B58" s="89"/>
+      <c r="C58" s="89"/>
+      <c r="D58" s="89"/>
+      <c r="E58" s="94"/>
+      <c r="F58" s="95"/>
+      <c r="G58" s="96"/>
+      <c r="H58" s="94"/>
+      <c r="I58" s="95"/>
+      <c r="J58" s="96"/>
     </row>
     <row r="59" ht="32" customHeight="1" spans="1:16">
-      <c r="A59" s="87"/>
-      <c r="B59" s="87"/>
-      <c r="C59" s="87"/>
-      <c r="D59" s="87"/>
-      <c r="E59" s="92"/>
-      <c r="F59" s="93"/>
-      <c r="G59" s="94"/>
-      <c r="H59" s="92"/>
-      <c r="I59" s="93"/>
-      <c r="J59" s="94"/>
+      <c r="A59" s="89"/>
+      <c r="B59" s="89"/>
+      <c r="C59" s="89"/>
+      <c r="D59" s="89"/>
+      <c r="E59" s="94"/>
+      <c r="F59" s="95"/>
+      <c r="G59" s="96"/>
+      <c r="H59" s="94"/>
+      <c r="I59" s="95"/>
+      <c r="J59" s="96"/>
     </row>
     <row r="60" ht="32" customHeight="1" spans="1:16">
-      <c r="A60" s="87"/>
-      <c r="B60" s="87"/>
-      <c r="C60" s="87"/>
-      <c r="D60" s="87"/>
-      <c r="E60" s="92"/>
-      <c r="F60" s="93"/>
-      <c r="G60" s="94"/>
-      <c r="H60" s="92"/>
-      <c r="I60" s="93"/>
-      <c r="J60" s="94"/>
+      <c r="A60" s="89"/>
+      <c r="B60" s="89"/>
+      <c r="C60" s="89"/>
+      <c r="D60" s="89"/>
+      <c r="E60" s="94"/>
+      <c r="F60" s="95"/>
+      <c r="G60" s="96"/>
+      <c r="H60" s="94"/>
+      <c r="I60" s="95"/>
+      <c r="J60" s="96"/>
     </row>
     <row r="61" ht="32" customHeight="1" spans="1:16">
-      <c r="A61" s="87"/>
-      <c r="B61" s="87"/>
-      <c r="C61" s="87"/>
-      <c r="D61" s="87"/>
-      <c r="E61" s="92"/>
-      <c r="F61" s="93"/>
-      <c r="G61" s="94"/>
-      <c r="H61" s="92"/>
-      <c r="I61" s="93"/>
-      <c r="J61" s="94"/>
+      <c r="A61" s="89"/>
+      <c r="B61" s="89"/>
+      <c r="C61" s="89"/>
+      <c r="D61" s="89"/>
+      <c r="E61" s="94"/>
+      <c r="F61" s="95"/>
+      <c r="G61" s="96"/>
+      <c r="H61" s="94"/>
+      <c r="I61" s="95"/>
+      <c r="J61" s="96"/>
     </row>
     <row r="62" ht="32" customHeight="1" spans="1:16">
-      <c r="A62" s="87"/>
-      <c r="B62" s="87"/>
-      <c r="C62" s="87"/>
-      <c r="D62" s="87"/>
-      <c r="E62" s="92"/>
-      <c r="F62" s="93"/>
-      <c r="G62" s="94"/>
-      <c r="H62" s="92"/>
-      <c r="I62" s="93"/>
-      <c r="J62" s="94"/>
+      <c r="A62" s="89"/>
+      <c r="B62" s="89"/>
+      <c r="C62" s="89"/>
+      <c r="D62" s="89"/>
+      <c r="E62" s="94"/>
+      <c r="F62" s="95"/>
+      <c r="G62" s="96"/>
+      <c r="H62" s="94"/>
+      <c r="I62" s="95"/>
+      <c r="J62" s="96"/>
     </row>
     <row r="63" ht="32" customHeight="1"/>
   </sheetData>
